--- a/SPOアップロード用.xlsx
+++ b/SPOアップロード用.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_84C2D4DF4D878022AD4D8C6C0987BDEB6D8109F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_49E2A040E41B85D9754D6EE1D18082F96D81318E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>タイトル</t>
   </si>
@@ -93,73 +93,64 @@
     <t>リリーフ工程</t>
   </si>
   <si>
-    <t>[{"OData_ストア": "Q10-A-11", "NONYUHIBIN": "2026063007", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 194, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-24", "NONYUHIBIN": "2026063007", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 443, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-B-5", "NONYUHIBIN": "2026063007", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 432, "番号": 3, "引取済": "未"}]</t>
+    <t>[{"OData_ストア": "Q10-A-12", "NONYUHIBIN": "2026070107", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 195, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-24", "NONYUHIBIN": "2026070107", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 443, "番号": 2, "引取済": "未"}]</t>
   </si>
   <si>
     <t>22:30</t>
   </si>
   <si>
-    <t>2026-06-30T06:59:48</t>
+    <t>2026-07-01T08:38:31</t>
   </si>
   <si>
     <t>山2</t>
   </si>
   <si>
-    <t>[{"OData_ストア": "Q10-A-10", "NONYUHIBIN": "2026063007", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 193, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-20", "NONYUHIBIN": "2026063007", "UKEIRE": "W5", "OData_納入先": "日野", "SEBANGO": 478, "番号": 2, "引取済": "未"}]</t>
-  </si>
-  <si>
-    <t>22:37</t>
+    <t>[{"OData_ストア": "Q10-A-10", "NONYUHIBIN": "2026070107", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 193, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-D-25", "NONYUHIBIN": "2026070107", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 437, "番号": 2, "引取済": "未"}]</t>
+  </si>
+  <si>
+    <t>22:36</t>
   </si>
   <si>
     <t>1工程</t>
   </si>
   <si>
-    <t>[{"OData_ストア": "Q10-A-13", "NONYUHIBIN": "2026063008", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 196, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-24", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 443, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-B-7", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 431, "番号": 3, "引取済": "未"}]</t>
-  </si>
-  <si>
-    <t>24:46</t>
-  </si>
-  <si>
-    <t>[{"OData_ストア": "Q10-A-11", "NONYUHIBIN": "2026063008", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 194, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-12", "NONYUHIBIN": "2026063008", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 195, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-B-5", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 432, "番号": 3, "引取済": "未"}]</t>
-  </si>
-  <si>
-    <t>24:53</t>
+    <t>[{"OData_ストア": "Q10-A-13", "NONYUHIBIN": "2026070108", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 196, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-24", "NONYUHIBIN": "2026070108", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 443, "番号": 2, "引取済": "未"}]</t>
+  </si>
+  <si>
+    <t>24:00</t>
+  </si>
+  <si>
+    <t>[{"OData_ストア": "Q10-A-11", "NONYUHIBIN": "2026070108", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 194, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-12", "NONYUHIBIN": "2026070108", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 195, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-B-5", "NONYUHIBIN": "2026070108", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 432, "番号": 3, "引取済": "未"}]</t>
+  </si>
+  <si>
+    <t>24:06</t>
   </si>
   <si>
     <t>山3</t>
   </si>
   <si>
-    <t>[{"OData_ストア": "Q10-D-23", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 438, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-D-25", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 437, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-D-25", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 437, "番号": 3, "引取済": "未"}]</t>
-  </si>
-  <si>
-    <t>25:03</t>
+    <t>[{"OData_ストア": "Q10-A-10", "NONYUHIBIN": "2026070108", "UKEIRE": "06", "OData_納入先": "日野", "SEBANGO": 193, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-D-23", "NONYUHIBIN": "2026070108", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 438, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-D-25", "NONYUHIBIN": "2026070108", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 437, "番号": 3, "引取済": "未"}]</t>
+  </si>
+  <si>
+    <t>24:16</t>
   </si>
   <si>
     <t>山4</t>
   </si>
   <si>
-    <t>[{"OData_ストア": "Q10-D-23", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 438, "番号": 1, "引取済": "未"}]</t>
-  </si>
-  <si>
-    <t>25:09</t>
+    <t>[{"OData_ストア": "Q10-A-20", "NONYUHIBIN": "2026070108", "UKEIRE": "W5", "OData_納入先": "日野", "SEBANGO": 478, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-22", "NONYUHIBIN": "2026070108", "UKEIRE": "W5", "OData_納入先": "日野", "SEBANGO": 477, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-B-1", "NONYUHIBIN": "2026070108", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 440, "番号": 3, "引取済": "未"}, {"OData_ストア": "Q10-B-A", "NONYUHIBIN": "2026070108", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 442, "番号": 4, "引取済": "未"}]</t>
+  </si>
+  <si>
+    <t>24:23</t>
   </si>
   <si>
     <t>山5</t>
   </si>
   <si>
-    <t>[{"OData_ストア": "Q10-A-20", "NONYUHIBIN": "2026063008", "UKEIRE": "W5", "OData_納入先": "日野", "SEBANGO": 478, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-A-22", "NONYUHIBIN": "2026063008", "UKEIRE": "W5", "OData_納入先": "日野", "SEBANGO": 477, "番号": 2, "引取済": "未"}, {"OData_ストア": "Q10-B-1", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 440, "番号": 3, "引取済": "未"}, {"OData_ストア": "Q10-B-3", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 439, "番号": 4, "引取済": "未"}]</t>
-  </si>
-  <si>
-    <t>25:18</t>
-  </si>
-  <si>
-    <t>山6</t>
-  </si>
-  <si>
-    <t>[{"OData_ストア": "Q10-A-27", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 250, "番号": 1, "引取済": "未"}, {"OData_ストア": "Q10-B-23", "NONYUHIBIN": "2026063008", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 248, "番号": 2, "引取済": "未"}]</t>
-  </si>
-  <si>
-    <t>25:25</t>
+    <t>[{"OData_ストア": "Q10-B-23", "NONYUHIBIN": "2026070108", "UKEIRE": "07", "OData_納入先": "日野", "SEBANGO": 248, "番号": 1, "引取済": "未"}]</t>
+  </si>
+  <si>
+    <t>24:34</t>
   </si>
 </sst>
 </file>
@@ -238,8 +229,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SPOExport" displayName="SPOExport" ref="A1:R9">
-  <autoFilter ref="A1:R9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SPOExport" displayName="SPOExport" ref="A1:R8">
+  <autoFilter ref="A1:R8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="タイトル"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="工程"/>
@@ -549,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -628,10 +619,10 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="I2" t="s">
         <v>21</v>
@@ -663,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>72.906999999999996</v>
+        <v>72.903000000000006</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -710,10 +701,10 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="I4" t="s">
         <v>28</v>
@@ -786,7 +777,7 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>62.190100000000001</v>
+        <v>72.903000000000006</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -795,7 +786,7 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
@@ -827,16 +818,16 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>62.19</v>
+        <v>72.908000000000001</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -868,16 +859,16 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>72.908000000000001</v>
+        <v>72.906000000000006</v>
       </c>
       <c r="F8">
         <v>7</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>478</v>
+        <v>313</v>
       </c>
       <c r="I8" t="s">
         <v>39</v>
@@ -892,47 +883,6 @@
         <v>22</v>
       </c>
       <c r="R8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9">
-        <v>72.91</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>368</v>
-      </c>
-      <c r="I9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -945,21 +895,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101004B6C44730FC23A4BAC59174F58A81E8C" ma:contentTypeVersion="4" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="17022af354609ec05e599673af6b3835">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9578c1f9-2eca-4bdd-815e-d7707635874e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f89407090e91fb4faffe42bdf8cbfe4" ns2:_="">
     <xsd:import namespace="9578c1f9-2eca-4bdd-815e-d7707635874e"/>
@@ -1103,14 +1038,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE9950ED-ADCC-4C7E-A96A-2A0CA1018269}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D920A4D6-8093-43EF-AB94-A5079FBD1118}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B81A3A1-782D-4561-A419-48A1F04D7760}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AAFBBE2-C9F1-4C12-A37A-E67A082AD126}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20AF6EE7-93F6-4919-9AA7-63CB60831378}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C578A9B-F376-4FE5-BB2D-1238FA11668A}"/>
 </file>